--- a/significance_results/sobol_sensitivity.xlsx
+++ b/significance_results/sobol_sensitivity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mattc\Documents\climate_detection_time\climate_detection_time\significance_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6819AB-DC62-4A91-8955-60887311243B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4DDED9-BF3C-43BE-BCFF-CF5560C4D239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="8820" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="30">
   <si>
     <t>ST</t>
   </si>
@@ -92,9 +92,6 @@
     <t>(with pre-whitening)</t>
   </si>
   <si>
-    <t>key</t>
-  </si>
-  <si>
     <t>ST - total order sensitivity</t>
   </si>
   <si>
@@ -102,6 +99,33 @@
   </si>
   <si>
     <t>S2 - second order (interaction) sensitivity</t>
+  </si>
+  <si>
+    <t>Water supply reliability</t>
+  </si>
+  <si>
+    <t>Upstream flood volume</t>
+  </si>
+  <si>
+    <t>RCP</t>
+  </si>
+  <si>
+    <t>GCM</t>
+  </si>
+  <si>
+    <t>LULC</t>
+  </si>
+  <si>
+    <t>RCP, GCM</t>
+  </si>
+  <si>
+    <t>RCP, LULC</t>
+  </si>
+  <si>
+    <t>GCM, LULC</t>
+  </si>
+  <si>
+    <t>Key</t>
   </si>
 </sst>
 </file>
@@ -111,7 +135,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,21 +163,6 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="6"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="6"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -191,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -219,26 +228,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,11 +522,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W42"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="6" max="6" width="12.69140625" customWidth="1"/>
+    <col min="10" max="10" width="20.84375" customWidth="1"/>
     <col min="11" max="11" width="10.61328125" customWidth="1"/>
+    <col min="15" max="15" width="12.15234375" customWidth="1"/>
     <col min="18" max="18" width="7.69140625" customWidth="1"/>
     <col min="21" max="21" width="9.4609375" customWidth="1"/>
   </cols>
@@ -720,23 +725,17 @@
       <c r="G9" s="17"/>
       <c r="H9" s="17"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="12"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
       <c r="W9" s="12"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.4">
@@ -761,30 +760,29 @@
         <v>9</v>
       </c>
       <c r="I10" s="12"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4" t="s">
+      <c r="J10" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4" t="s">
+      <c r="O10" s="13"/>
+      <c r="P10" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="Q10" s="13" t="s">
         <v>9</v>
       </c>
       <c r="R10" s="12"/>
-      <c r="S10" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="T10" s="7"/>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
@@ -816,8 +814,8 @@
         <v>6.9097927000000003E-2</v>
       </c>
       <c r="I11" s="12"/>
-      <c r="J11" s="4" t="s">
-        <v>4</v>
+      <c r="J11" s="15" t="s">
+        <v>23</v>
       </c>
       <c r="K11" s="5">
         <v>0.53749362890832897</v>
@@ -832,7 +830,7 @@
         <v>6.3527682000000002E-2</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="P11" s="5">
         <v>0.49672428483253001</v>
@@ -841,9 +839,6 @@
         <v>8.6742059675317895E-2</v>
       </c>
       <c r="R11" s="12"/>
-      <c r="S11" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -875,8 +870,8 @@
         <v>7.1049068000000007E-2</v>
       </c>
       <c r="I12" s="12"/>
-      <c r="J12" s="4" t="s">
-        <v>5</v>
+      <c r="J12" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="K12" s="5">
         <v>0.97055671591946102</v>
@@ -891,7 +886,7 @@
         <v>8.1593476999999998E-2</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="P12" s="5">
         <v>-8.2987022004007895E-3</v>
@@ -900,9 +895,6 @@
         <v>8.2693333038782693E-2</v>
       </c>
       <c r="R12" s="12"/>
-      <c r="S12" s="7" t="s">
-        <v>21</v>
-      </c>
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
@@ -934,8 +926,8 @@
         <v>0.14237645700000001</v>
       </c>
       <c r="I13" s="12"/>
-      <c r="J13" s="4" t="s">
-        <v>6</v>
+      <c r="J13" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="K13" s="5">
         <v>0.10652969873841101</v>
@@ -950,7 +942,7 @@
         <v>2.5772494E-2</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P13" s="5">
         <v>2.3168946466166399E-3</v>
@@ -975,8 +967,10 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
+      <c r="J14" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="12"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -1000,8 +994,10 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="12"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
+      <c r="J15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" s="10"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -1027,21 +1023,21 @@
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="12"/>
-      <c r="J16" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="20"/>
-      <c r="V16" s="20"/>
+      <c r="J16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="8"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
       <c r="W16" s="12"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.4">
@@ -1066,26 +1062,16 @@
         <v>9</v>
       </c>
       <c r="I17" s="12"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q17" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="J17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="9"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
       <c r="R17" s="12"/>
       <c r="S17" s="12"/>
       <c r="T17" s="12"/>
@@ -1119,30 +1105,14 @@
         <v>6.5367032000000005E-2</v>
       </c>
       <c r="I18" s="12"/>
-      <c r="J18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="5">
-        <v>0.30385594199999999</v>
-      </c>
-      <c r="L18" s="5">
-        <v>3.4626513999999997E-2</v>
-      </c>
-      <c r="M18" s="5">
-        <v>1.3627450000000001E-3</v>
-      </c>
-      <c r="N18" s="5">
-        <v>4.4950726000000003E-2</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P18" s="5">
-        <v>0.29742570099999999</v>
-      </c>
-      <c r="Q18" s="5">
-        <v>5.7581611999999997E-2</v>
-      </c>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
       <c r="T18" s="12"/>
@@ -1176,29 +1146,27 @@
         <v>5.8638389999999999E-2</v>
       </c>
       <c r="I19" s="12"/>
-      <c r="J19" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K19" s="5">
-        <v>1.011847908</v>
-      </c>
-      <c r="L19" s="5">
-        <v>6.5518191000000003E-2</v>
-      </c>
-      <c r="M19" s="5">
-        <v>0.67439900900000005</v>
-      </c>
-      <c r="N19" s="5">
-        <v>8.4019813999999998E-2</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="P19" s="5">
-        <v>-3.5289289000000001E-2</v>
-      </c>
-      <c r="Q19" s="5">
-        <v>5.3919348999999998E-2</v>
+      <c r="J19" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
@@ -1233,29 +1201,29 @@
         <v>9.2127301999999994E-2</v>
       </c>
       <c r="I20" s="12"/>
-      <c r="J20" s="4" t="s">
-        <v>6</v>
+      <c r="J20" s="15" t="s">
+        <v>23</v>
       </c>
       <c r="K20" s="5">
-        <v>4.508003E-3</v>
+        <v>0.30385594199999999</v>
       </c>
       <c r="L20" s="5">
-        <v>4.6548359999999999E-3</v>
+        <v>3.4626513999999997E-2</v>
       </c>
       <c r="M20" s="5">
-        <v>-2.5673639999999999E-3</v>
+        <v>1.3627450000000001E-3</v>
       </c>
       <c r="N20" s="5">
-        <v>3.7777919999999999E-3</v>
+        <v>4.4950726000000003E-2</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="P20" s="5">
-        <v>1.8463539999999999E-3</v>
+        <v>0.29742570099999999</v>
       </c>
       <c r="Q20" s="5">
-        <v>8.5729537999999994E-2</v>
+        <v>5.7581611999999997E-2</v>
       </c>
       <c r="R20" s="12"/>
       <c r="S20" s="12"/>
@@ -1266,14 +1234,30 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.4">
       <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
+      <c r="J21" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="5">
+        <v>1.011847908</v>
+      </c>
+      <c r="L21" s="5">
+        <v>6.5518191000000003E-2</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0.67439900900000005</v>
+      </c>
+      <c r="N21" s="5">
+        <v>8.4019813999999998E-2</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21" s="5">
+        <v>-3.5289289000000001E-2</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>5.3919348999999998E-2</v>
+      </c>
       <c r="R21" s="12"/>
       <c r="S21" s="12"/>
       <c r="T21" s="12"/>
@@ -1283,14 +1267,30 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.4">
       <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
+      <c r="J22" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" s="5">
+        <v>4.508003E-3</v>
+      </c>
+      <c r="L22" s="5">
+        <v>4.6548359999999999E-3</v>
+      </c>
+      <c r="M22" s="5">
+        <v>-2.5673639999999999E-3</v>
+      </c>
+      <c r="N22" s="5">
+        <v>3.7777919999999999E-3</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="5">
+        <v>1.8463539999999999E-3</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>8.5729537999999994E-2</v>
+      </c>
       <c r="R22" s="12"/>
       <c r="S22" s="12"/>
       <c r="T22" s="12"/>
@@ -1310,14 +1310,14 @@
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
       <c r="I23" s="12"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
       <c r="S23" s="12"/>
       <c r="T23" s="12"/>
@@ -1347,14 +1347,16 @@
         <v>9</v>
       </c>
       <c r="I24" s="12"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
+      <c r="J24" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
       <c r="R24" s="12"/>
       <c r="S24" s="12"/>
       <c r="T24" s="12"/>
@@ -1388,14 +1390,16 @@
         <v>9.9805788403229706E-2</v>
       </c>
       <c r="I25" s="12"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
+      <c r="J25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
       <c r="R25" s="12"/>
       <c r="S25" s="12"/>
       <c r="T25" s="12"/>
@@ -1428,14 +1432,16 @@
         <v>6.4632625152124604E-2</v>
       </c>
       <c r="I26" s="12"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
+      <c r="J26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
       <c r="R26" s="12"/>
       <c r="S26" s="12"/>
       <c r="T26" s="12"/>
@@ -1467,28 +1473,213 @@
         <v>0.110977851242927</v>
       </c>
       <c r="I27" s="12"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
+      <c r="J27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
       <c r="R27" s="12"/>
       <c r="S27" s="12"/>
       <c r="T27" s="12"/>
       <c r="U27" s="12"/>
     </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+    </row>
+    <row r="33" spans="8:19" x14ac:dyDescent="0.4">
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="12"/>
+      <c r="R33" s="12"/>
+      <c r="S33" s="12"/>
+    </row>
+    <row r="34" spans="8:19" x14ac:dyDescent="0.4">
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="12"/>
+      <c r="Q34" s="12"/>
+      <c r="R34" s="12"/>
+      <c r="S34" s="12"/>
+    </row>
+    <row r="35" spans="8:19" x14ac:dyDescent="0.4">
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="12"/>
+      <c r="S35" s="12"/>
+    </row>
+    <row r="36" spans="8:19" x14ac:dyDescent="0.4">
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="12"/>
+      <c r="P36" s="12"/>
+      <c r="Q36" s="12"/>
+    </row>
+    <row r="37" spans="8:19" x14ac:dyDescent="0.4">
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="12"/>
+      <c r="P37" s="12"/>
+      <c r="Q37" s="12"/>
+    </row>
+    <row r="38" spans="8:19" x14ac:dyDescent="0.4">
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="12"/>
+      <c r="P38" s="12"/>
+      <c r="Q38" s="12"/>
+    </row>
+    <row r="39" spans="8:19" x14ac:dyDescent="0.4">
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="12"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="12"/>
+      <c r="P39" s="12"/>
+      <c r="Q39" s="12"/>
+    </row>
+    <row r="40" spans="8:19" x14ac:dyDescent="0.4">
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="12"/>
+      <c r="P40" s="12"/>
+      <c r="Q40" s="12"/>
+    </row>
+    <row r="41" spans="8:19" x14ac:dyDescent="0.4">
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="12"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="12"/>
+      <c r="P41" s="12"/>
+      <c r="Q41" s="12"/>
+    </row>
+    <row r="42" spans="8:19" x14ac:dyDescent="0.4">
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+      <c r="M42" s="12"/>
+      <c r="N42" s="12"/>
+      <c r="O42" s="12"/>
+      <c r="P42" s="12"/>
+      <c r="Q42" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="4">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="J9:Q9"/>
-    <mergeCell ref="J16:Q16"/>
-    <mergeCell ref="J23:Q23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
